--- a/sheets/대금율보/검수/각시조.xlsx
+++ b/sheets/대금율보/검수/각시조.xlsx
@@ -5187,8 +5187,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -5196,8 +5195,7 @@
         <is>
           <t xml:space="preserve">–
 –
-黃И
-‹</t>
+黃И</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -5209,22 +5207,19 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -5232,18 +5227,13 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-黃И
-‹</t>
+黃И</t>
         </is>
       </c>
       <c r="O7" s="22"/>
       <c r="P7" s="21"/>
       <c r="Q7" s="22"/>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R7" s="21"/>
       <c r="S7" s="22"/>
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
@@ -5424,8 +5414,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">И
-‹</t>
+          <t xml:space="preserve">И</t>
         </is>
       </c>
       <c r="E10" s="22"/>
@@ -5484,8 +5473,7 @@
       </c>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="S10" s="22"/>
@@ -5498,8 +5486,7 @@
         <is>
           <t xml:space="preserve">仲
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -5515,8 +5502,7 @@
       <c r="E11" s="22"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="G11" s="22"/>
@@ -5605,8 +5591,7 @@
         <is>
           <t xml:space="preserve">–
 –
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -5626,8 +5611,7 @@
         <is>
           <t xml:space="preserve">–
 –
-汰)
-‹</t>
+汰)</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -5651,8 +5635,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -5660,8 +5643,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -5797,8 +5779,7 @@
         <is>
           <t xml:space="preserve">黃И
 仲И
-太∧
-‹</t>
+太∧</t>
         </is>
       </c>
       <c r="E14" s="22"/>
@@ -5910,8 +5891,7 @@
         <is>
           <t xml:space="preserve">太И
 黃⌇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -5923,8 +5903,7 @@
         <is>
           <t xml:space="preserve">太И
 黃⌇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -5936,8 +5915,7 @@
         <is>
           <t xml:space="preserve">㑲太
 黃⌇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="O15" s="22"/>
@@ -5945,8 +5923,7 @@
         <is>
           <t xml:space="preserve">黃∧
 –И
-㑲
-‹</t>
+㑲</t>
         </is>
       </c>
       <c r="Q15" s="22" t="inlineStr">

--- a/sheets/대금율보/검수/각시조.xlsx
+++ b/sheets/대금율보/검수/각시조.xlsx
@@ -4766,32 +4766,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="128.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="128.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="128.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="128.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="128.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="128.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="128.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="128.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="128.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="128.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="128.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="128.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="128.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
     </row>
-    <row r="16">
+    <row r="16" ht="6.0" customHeight="true">
       <c r="A16" s="0"/>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="93.02" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="20" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
       <c r="T17" s="20"/>
       <c r="U17" s="20"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="128.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="128.04" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="128.04" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="128.04" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="128.04" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="U22" s="22"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="128.04" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="128.04" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="22"/>
@@ -6175,7 +6175,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="22"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="128.04" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -6198,7 +6198,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="128.04" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6221,7 +6221,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="128.04" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
@@ -6244,7 +6244,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="128.04" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
@@ -6267,7 +6267,7 @@
       <c r="T28" s="21"/>
       <c r="U28" s="22"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="128.04" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -6290,7 +6290,7 @@
       <c r="T29" s="21"/>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="128.04" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
@@ -6320,7 +6320,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="15" max="16383" man="1"/>
   </rowBreaks>
